--- a/SuppXLS/Scen_RES_SHARE_50%_24_7.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_50%_24_7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT_FULL\SuppXLS\Policy_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Desktop\Uni\Energy modelling\Times laboratory\MSc_SELECT-main\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2FAE5B-B617-4B04-848A-288BA6E5BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937BD294-CA2A-4A9B-BA70-2ED2963C901B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INS_1" sheetId="11" r:id="rId1"/>
@@ -82,19 +82,19 @@
     <t>ELC_GRID_RES</t>
   </si>
   <si>
-    <t>FX</t>
-  </si>
-  <si>
     <t>NL</t>
   </si>
   <si>
     <t>ELC_FIN_DEM</t>
   </si>
   <si>
-    <t>FLO_SHAR</t>
+    <t>LO</t>
   </si>
   <si>
-    <t>ANNUAL</t>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>USER_CONSTRAINT</t>
   </si>
 </sst>
 </file>
@@ -4442,15 +4442,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" customWidth="1"/>
     <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9">
@@ -4462,7 +4462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="15.75" thickBot="1">
+    <row r="5" spans="2:9" ht="15" thickBot="1">
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
@@ -4482,27 +4482,27 @@
         <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2">
-        <v>2030</v>
+        <v>2050</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H6" s="5">
         <v>0.5</v>

--- a/SuppXLS/Scen_RES_SHARE_50%_24_7.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_50%_24_7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Desktop\Uni\Energy modelling\Times laboratory\MSc_SELECT-main\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937BD294-CA2A-4A9B-BA70-2ED2963C901B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F32AEAB-A2A2-4AAC-9D07-04DEB4DF1F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,9 +73,6 @@
     <t>LimType</t>
   </si>
   <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
     <t>TimeSlice</t>
   </si>
   <si>
@@ -95,6 +92,9 @@
   </si>
   <si>
     <t>USER_CONSTRAINT</t>
+  </si>
+  <si>
+    <t>~UC_T</t>
   </si>
 </sst>
 </file>
@@ -4459,12 +4459,12 @@
     <row r="2" spans="2:9"/>
     <row r="4" spans="2:9">
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1">
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -4482,27 +4482,27 @@
         <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2">
         <v>2050</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="5">
         <v>0.5</v>

--- a/SuppXLS/Scen_RES_SHARE_50%_24_7.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_50%_24_7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Desktop\Uni\Energy modelling\Times laboratory\MSc_SELECT-main\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT_FULL\SuppXLS\Policy_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F32AEAB-A2A2-4AAC-9D07-04DEB4DF1F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2FAE5B-B617-4B04-848A-288BA6E5BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INS_1" sheetId="11" r:id="rId1"/>
@@ -73,10 +73,16 @@
     <t>LimType</t>
   </si>
   <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
     <t>TimeSlice</t>
   </si>
   <si>
     <t>ELC_GRID_RES</t>
+  </si>
+  <si>
+    <t>FX</t>
   </si>
   <si>
     <t>NL</t>
@@ -85,16 +91,10 @@
     <t>ELC_FIN_DEM</t>
   </si>
   <si>
-    <t>LO</t>
+    <t>FLO_SHAR</t>
   </si>
   <si>
-    <t>DAYNITE</t>
-  </si>
-  <si>
-    <t>USER_CONSTRAINT</t>
-  </si>
-  <si>
-    <t>~UC_T</t>
+    <t>ANNUAL</t>
   </si>
 </sst>
 </file>
@@ -4442,15 +4442,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.1796875" customWidth="1"/>
-    <col min="4" max="4" width="18.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
     <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9">
@@ -4459,12 +4459,12 @@
     <row r="2" spans="2:9"/>
     <row r="4" spans="2:9">
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="15" thickBot="1">
+    <row r="5" spans="2:9" ht="15.75" thickBot="1">
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -4482,27 +4482,27 @@
         <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="2">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6" s="5">
         <v>0.5</v>
